--- a/data/dividends_info_20260709.xlsx
+++ b/data/dividends_info_20260709.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60.81000137329102</v>
+        <v>62.68000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1480019700172706</v>
+        <v>0.1435864702645323</v>
       </c>
       <c r="J2" t="n">
         <v>249</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.80000305175781</v>
+        <v>64.65000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.080246862705991</v>
+        <v>1.082753261374318</v>
       </c>
       <c r="J3" t="n">
         <v>228</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.859999656677246</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6085192909653669</v>
+        <v>0.6122448860432199</v>
       </c>
       <c r="J4" t="n">
         <v>158</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>60.81000137329102</v>
+        <v>62.68000030517578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1480019700172706</v>
+        <v>0.1435864702645323</v>
       </c>
       <c r="J6" t="n">
         <v>158</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.089999914169312</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.68421067761643</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J7" t="n">
         <v>137</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.06999969482422</v>
+        <v>21.0049991607666</v>
       </c>
       <c r="I8" t="n">
-        <v>1.281442828242303</v>
+        <v>1.285408287491434</v>
       </c>
       <c r="J8" t="n">
         <v>137</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.059999942779541</v>
+        <v>6.03000020980835</v>
       </c>
       <c r="I9" t="n">
-        <v>3.300330064166073</v>
+        <v>3.31674947000303</v>
       </c>
       <c r="J9" t="n">
         <v>130</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.599999904632568</v>
+        <v>7.25</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7894736941171157</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="J10" t="n">
         <v>102</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.949999809265137</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J13" t="n">
         <v>81</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.06999969482422</v>
+        <v>21.0049991607666</v>
       </c>
       <c r="I14" t="n">
-        <v>1.281442828242303</v>
+        <v>1.285408287491434</v>
       </c>
       <c r="J14" t="n">
         <v>74</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>60.81000137329102</v>
+        <v>62.68000030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1480019700172706</v>
+        <v>0.1435864702645323</v>
       </c>
       <c r="J15" t="n">
         <v>74</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.949999809265137</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J18" t="n">
         <v>25</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.840000152587891</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I19" t="n">
-        <v>4.280821805958635</v>
+        <v>4.302926032050844</v>
       </c>
       <c r="J19" t="n">
         <v>18</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.150000095367432</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="I20" t="n">
-        <v>3.373493898380374</v>
+        <v>3.30969265647107</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.12600040435791</v>
+        <v>10.07999992370605</v>
       </c>
       <c r="I21" t="n">
-        <v>2.567647537206341</v>
+        <v>2.579365098887891</v>
       </c>
       <c r="J21" t="n">
         <v>11</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.52000045776367</v>
+        <v>14.77999973297119</v>
       </c>
       <c r="I22" t="n">
-        <v>4.132231274684204</v>
+        <v>4.059539992152512</v>
       </c>
       <c r="J22" t="n">
         <v>11</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.783999919891357</v>
+        <v>2.778000116348267</v>
       </c>
       <c r="I23" t="n">
-        <v>7.902299077960651</v>
+        <v>7.919366119004851</v>
       </c>
       <c r="J23" t="n">
         <v>11</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.64999961853027</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>1.91348604223598</v>
+        <v>1.89420651271625</v>
       </c>
       <c r="J26" t="n">
         <v>11</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.829999923706055</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I28" t="n">
-        <v>2.058319066387184</v>
+        <v>2.061855609288493</v>
       </c>
       <c r="J28" t="n">
         <v>4</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.299999952316284</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="I30" t="n">
-        <v>4.545454611134596</v>
+        <v>4.518072380004178</v>
       </c>
       <c r="J30" t="n">
         <v>4</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.639999866485596</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="I32" t="n">
-        <v>1.508620733065215</v>
+        <v>1.489361762568769</v>
       </c>
       <c r="J32" t="n">
         <v>-3</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>35.09999847412109</v>
+        <v>35.04999923706055</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4273504459283485</v>
+        <v>0.4279600663768223</v>
       </c>
       <c r="J33" t="n">
         <v>-3</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9.699999809265137</v>
+        <v>9.550000190734863</v>
       </c>
       <c r="I34" t="n">
-        <v>23.01958808150907</v>
+        <v>23.38115136548684</v>
       </c>
       <c r="J34" t="n">
         <v>-3</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.199999809265137</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.7766990147433418</v>
       </c>
       <c r="J35" t="n">
         <v>-10</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>21.68000030517578</v>
+        <v>21.44000053405762</v>
       </c>
       <c r="I36" t="n">
-        <v>1.153136515133333</v>
+        <v>1.166044747073923</v>
       </c>
       <c r="J36" t="n">
         <v>-17</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>28.45000076293945</v>
+        <v>28.70000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6854129868917888</v>
+        <v>0.6794424906490076</v>
       </c>
       <c r="J37" t="n">
         <v>-17</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.860000014305115</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="I38" t="n">
-        <v>1.774193534741913</v>
+        <v>1.764705877853063</v>
       </c>
       <c r="J38" t="n">
         <v>-17</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.070000171661377</v>
+        <v>5.125</v>
       </c>
       <c r="I39" t="n">
-        <v>5.719920910869921</v>
+        <v>5.658536585365853</v>
       </c>
       <c r="J39" t="n">
         <v>-17</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.53600001335144</v>
+        <v>2.529999971389771</v>
       </c>
       <c r="I41" t="n">
-        <v>5.465299655769076</v>
+        <v>5.478260931515535</v>
       </c>
       <c r="J41" t="n">
         <v>-17</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>51.86999893188477</v>
+        <v>52.18999862670898</v>
       </c>
       <c r="I42" t="n">
-        <v>1.214574923796144</v>
+        <v>1.207127834024484</v>
       </c>
       <c r="J42" t="n">
         <v>-17</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.204999923706055</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="I43" t="n">
-        <v>2.256244991480715</v>
+        <v>2.254428327536294</v>
       </c>
       <c r="J43" t="n">
         <v>-17</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>16.60000038146973</v>
+        <v>16.75</v>
       </c>
       <c r="I44" t="n">
-        <v>4.698795072744092</v>
+        <v>4.656716417910448</v>
       </c>
       <c r="J44" t="n">
         <v>-17</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>28.85000038146973</v>
+        <v>28.72999954223633</v>
       </c>
       <c r="I45" t="n">
-        <v>2.946273791198812</v>
+        <v>2.958579928796742</v>
       </c>
       <c r="J45" t="n">
         <v>-17</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>60.81000137329102</v>
+        <v>62.68000030517578</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1480019700172706</v>
+        <v>0.1435864702645323</v>
       </c>
       <c r="J46" t="n">
         <v>-17</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.409999966621399</v>
+        <v>1.429999947547913</v>
       </c>
       <c r="I47" t="n">
-        <v>0.709219874945225</v>
+        <v>0.699300724950897</v>
       </c>
       <c r="J47" t="n">
         <v>-17</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>6.251999855041504</v>
+        <v>6.184000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>2.899872108183157</v>
+        <v>2.931759371808684</v>
       </c>
       <c r="J48" t="n">
         <v>-17</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.439999580383301</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="I49" t="n">
-        <v>2.754237410563984</v>
+        <v>2.725366887208018</v>
       </c>
       <c r="J49" t="n">
         <v>-17</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10.20499992370605</v>
+        <v>10.19499969482422</v>
       </c>
       <c r="I50" t="n">
-        <v>2.714355728279168</v>
+        <v>2.717018227480938</v>
       </c>
       <c r="J50" t="n">
         <v>-17</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.134999990463257</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="I51" t="n">
-        <v>1.189427322769395</v>
+        <v>1.173913067815886</v>
       </c>
       <c r="J51" t="n">
         <v>-24</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.924000024795532</v>
+        <v>2.953999996185303</v>
       </c>
       <c r="I52" t="n">
-        <v>3.761969872339246</v>
+        <v>3.723764392080241</v>
       </c>
       <c r="J52" t="n">
         <v>-24</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.679999947547913</v>
+        <v>1.649999976158142</v>
       </c>
       <c r="I53" t="n">
-        <v>1.428571473173545</v>
+        <v>1.454545475563071</v>
       </c>
       <c r="J53" t="n">
         <v>-24</v>
@@ -2943,7 +2943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:C230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3986,7 +3986,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4013,14 +4013,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4251,14 +4251,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4285,14 +4285,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4336,14 +4336,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4387,14 +4387,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4438,14 +4438,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4540,14 +4540,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4574,14 +4574,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4676,14 +4676,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4693,14 +4693,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4727,14 +4727,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4778,14 +4778,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4795,14 +4795,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4846,14 +4846,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4863,14 +4863,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4880,14 +4880,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4931,14 +4931,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4965,14 +4965,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5040,7 +5040,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5091,7 +5091,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5152,14 +5152,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5176,7 +5176,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5193,7 +5193,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5210,7 +5210,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5254,14 +5254,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5322,14 +5322,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5380,7 +5380,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5390,14 +5390,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5424,14 +5424,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5448,7 +5448,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5465,7 +5465,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5509,14 +5509,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5533,7 +5533,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5560,14 +5560,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5584,7 +5584,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5594,14 +5594,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5645,14 +5645,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5669,7 +5669,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5696,14 +5696,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5713,14 +5713,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5730,14 +5730,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5747,14 +5747,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5788,7 +5788,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5798,14 +5798,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5815,14 +5815,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5832,14 +5832,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5866,14 +5866,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5907,7 +5907,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5934,14 +5934,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5958,7 +5958,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6026,46 +6026,46 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6077,12 +6077,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6094,12 +6094,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6111,29 +6111,29 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6145,29 +6145,29 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6179,12 +6179,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6196,7 +6196,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6213,7 +6213,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6257,14 +6257,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6274,14 +6274,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6315,7 +6315,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6349,46 +6349,46 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6400,12 +6400,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6417,12 +6417,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6434,12 +6434,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6451,75 +6451,75 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6553,7 +6553,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6563,14 +6563,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6580,14 +6580,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6638,29 +6638,29 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6672,17 +6672,187 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
+          <t>F.I.L.A. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Bper Banca S.P.A.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BANCA SISTEMA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>BANCA SISTEMA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Abitare In S.p.A.</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Unipol S.p.A.</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
           <t>EMAK S.p.A.</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Riba Mundo Tecnologia S.A.</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
